--- a/Data_clean/MCAS/Estados_US/Edos_USA_2015/NORTH_DAKOTA_2015.xlsx
+++ b/Data_clean/MCAS/Estados_US/Edos_USA_2015/NORTH_DAKOTA_2015.xlsx
@@ -351,28 +351,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D124"/>
+  <dimension ref="A1:D118"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
@@ -395,6 +395,11 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>Total</t>
@@ -426,6 +431,11 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>Mexicali</t>
@@ -439,6 +449,11 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>Tijuana</t>
@@ -452,6 +467,11 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>Total</t>
@@ -483,6 +503,11 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>Ostuacán</t>
@@ -496,6 +521,11 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>Total</t>
@@ -527,6 +557,11 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
           <t>Guerrero</t>
@@ -540,6 +575,11 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
           <t>Nuevo Casas Grandes</t>
@@ -553,6 +593,11 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>Total</t>
@@ -584,6 +629,11 @@
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>Total</t>
@@ -599,7 +649,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ciudad de México</t>
+          <t>Ciudad De México</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -615,6 +665,11 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>Iztacalco</t>
@@ -628,6 +683,11 @@
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>Iztapalapa</t>
@@ -641,6 +701,11 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>Miguel Hidalgo</t>
@@ -654,6 +719,11 @@
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>Venustiano Carranza</t>
@@ -667,6 +737,11 @@
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>Total</t>
@@ -698,6 +773,11 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
           <t>Durango</t>
@@ -711,6 +791,11 @@
       </c>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
           <t>Guadalupe Victoria</t>
@@ -724,6 +809,11 @@
       </c>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>Pueblo Nuevo</t>
@@ -737,6 +827,11 @@
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>Total</t>
@@ -752,7 +847,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Estado de México</t>
+          <t>Estado De México</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -768,9 +863,14 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Ecatepec de Morelos</t>
+          <t>Ecatepec De Morelos</t>
         </is>
       </c>
       <c r="C29">
@@ -781,6 +881,11 @@
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
           <t>Tejupilco</t>
@@ -794,6 +899,11 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>Texcoco</t>
@@ -807,9 +917,14 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Tlalnepantla de Baz</t>
+          <t>Tlalnepantla De Baz</t>
         </is>
       </c>
       <c r="C32">
@@ -820,6 +935,11 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>Total</t>
@@ -840,7 +960,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Apaseo el Grande</t>
+          <t>Apaseo El Grande</t>
         </is>
       </c>
       <c r="C34">
@@ -851,6 +971,11 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
           <t>Irapuato</t>
@@ -864,6 +989,11 @@
       </c>
     </row>
     <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
           <t>Salvatierra</t>
@@ -877,6 +1007,11 @@
       </c>
     </row>
     <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
           <t>San Felipe</t>
@@ -890,6 +1025,11 @@
       </c>
     </row>
     <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
           <t>Victoria</t>
@@ -903,6 +1043,11 @@
       </c>
     </row>
     <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>Yuriria</t>
@@ -916,6 +1061,11 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>Total</t>
@@ -936,7 +1086,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Acapulco de Juárez</t>
+          <t>Acapulco De Juárez</t>
         </is>
       </c>
       <c r="C41">
@@ -947,6 +1097,11 @@
       </c>
     </row>
     <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
           <t>Leonardo Bravo</t>
@@ -960,6 +1115,11 @@
       </c>
     </row>
     <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>Ometepec</t>
@@ -973,6 +1133,11 @@
       </c>
     </row>
     <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1004,6 +1169,11 @@
       </c>
     </row>
     <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B46" t="inlineStr">
         <is>
           <t>Ixmiquilpan</t>
@@ -1017,9 +1187,14 @@
       </c>
     </row>
     <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Tula de Allende</t>
+          <t>Tula De Allende</t>
         </is>
       </c>
       <c r="C47">
@@ -1030,6 +1205,11 @@
       </c>
     </row>
     <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1061,6 +1241,11 @@
       </c>
     </row>
     <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
           <t>La Huerta</t>
@@ -1074,9 +1259,14 @@
       </c>
     </row>
     <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Lagos de Moreno</t>
+          <t>Lagos De Moreno</t>
         </is>
       </c>
       <c r="C51">
@@ -1087,6 +1277,11 @@
       </c>
     </row>
     <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
           <t>Teocaltiche</t>
@@ -1100,9 +1295,14 @@
       </c>
     </row>
     <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Tepatitlán de Morelos</t>
+          <t>Tepatitlán De Morelos</t>
         </is>
       </c>
       <c r="C53">
@@ -1113,6 +1313,11 @@
       </c>
     </row>
     <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
           <t>Villa Hidalgo</t>
@@ -1126,6 +1331,11 @@
       </c>
     </row>
     <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1157,6 +1367,11 @@
       </c>
     </row>
     <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B57" t="inlineStr">
         <is>
           <t>Tangancícuaro</t>
@@ -1170,6 +1385,11 @@
       </c>
     </row>
     <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
           <t>Tarímbaro</t>
@@ -1183,6 +1403,11 @@
       </c>
     </row>
     <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
           <t>Tuzantla</t>
@@ -1196,6 +1421,11 @@
       </c>
     </row>
     <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
           <t>Uruapan</t>
@@ -1209,6 +1439,11 @@
       </c>
     </row>
     <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1240,6 +1475,11 @@
       </c>
     </row>
     <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B63" t="inlineStr">
         <is>
           <t>Mazatepec</t>
@@ -1253,6 +1493,11 @@
       </c>
     </row>
     <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
           <t>Tlaquiltenango</t>
@@ -1266,6 +1511,11 @@
       </c>
     </row>
     <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B65" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1297,6 +1547,11 @@
       </c>
     </row>
     <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B67" t="inlineStr">
         <is>
           <t>Ruíz</t>
@@ -1310,6 +1565,11 @@
       </c>
     </row>
     <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B68" t="inlineStr">
         <is>
           <t>San Blas</t>
@@ -1323,6 +1583,11 @@
       </c>
     </row>
     <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
           <t>Santiago Ixcuintla</t>
@@ -1336,6 +1601,11 @@
       </c>
     </row>
     <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1367,6 +1637,11 @@
       </c>
     </row>
     <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr">
         <is>
           <t>Doctor González</t>
@@ -1380,6 +1655,11 @@
       </c>
     </row>
     <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
           <t>Monterrey</t>
@@ -1393,6 +1673,11 @@
       </c>
     </row>
     <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1413,7 +1698,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Nejapa de Madero</t>
+          <t>Nejapa De Madero</t>
         </is>
       </c>
       <c r="C75">
@@ -1424,6 +1709,11 @@
       </c>
     </row>
     <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
           <t>San Antonino Monte Verde</t>
@@ -1437,6 +1727,11 @@
       </c>
     </row>
     <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
           <t>San Bartolomé Quialana</t>
@@ -1450,6 +1745,11 @@
       </c>
     </row>
     <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
           <t>San Sebastián Nicananduta</t>
@@ -1463,6 +1763,11 @@
       </c>
     </row>
     <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B79" t="inlineStr">
         <is>
           <t>Santo Domingo Teojomulco</t>
@@ -1476,6 +1781,11 @@
       </c>
     </row>
     <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B80" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1507,6 +1817,11 @@
       </c>
     </row>
     <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B82" t="inlineStr">
         <is>
           <t>Pantepec</t>
@@ -1520,6 +1835,11 @@
       </c>
     </row>
     <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B83" t="inlineStr">
         <is>
           <t>Tehuacán</t>
@@ -1533,6 +1853,11 @@
       </c>
     </row>
     <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B84" t="inlineStr">
         <is>
           <t>Tlachichuca</t>
@@ -1546,6 +1871,11 @@
       </c>
     </row>
     <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B85" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1577,6 +1907,11 @@
       </c>
     </row>
     <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B87" t="inlineStr">
         <is>
           <t>Querétaro</t>
@@ -1590,9 +1925,14 @@
       </c>
     </row>
     <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>San Juan del Río</t>
+          <t>San Juan Del Río</t>
         </is>
       </c>
       <c r="C88">
@@ -1603,6 +1943,11 @@
       </c>
     </row>
     <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B89" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1634,6 +1979,11 @@
       </c>
     </row>
     <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Quintana Roo</t>
+        </is>
+      </c>
       <c r="B91" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1665,9 +2015,14 @@
       </c>
     </row>
     <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Villa de Ramos</t>
+          <t>Villa De Ramos</t>
         </is>
       </c>
       <c r="C93">
@@ -1678,6 +2033,11 @@
       </c>
     </row>
     <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B94" t="inlineStr">
         <is>
           <t>Villa Juárez</t>
@@ -1691,6 +2051,11 @@
       </c>
     </row>
     <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B95" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1722,6 +2087,11 @@
       </c>
     </row>
     <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B97" t="inlineStr">
         <is>
           <t>Elota</t>
@@ -1735,6 +2105,11 @@
       </c>
     </row>
     <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B98" t="inlineStr">
         <is>
           <t>Navolato</t>
@@ -1748,6 +2123,11 @@
       </c>
     </row>
     <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B99" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1779,6 +2159,11 @@
       </c>
     </row>
     <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B101" t="inlineStr">
         <is>
           <t>Navojoa</t>
@@ -1792,6 +2177,11 @@
       </c>
     </row>
     <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B102" t="inlineStr">
         <is>
           <t>Nogales</t>
@@ -1805,6 +2195,11 @@
       </c>
     </row>
     <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B103" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1836,6 +2231,11 @@
       </c>
     </row>
     <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B105" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1867,6 +2267,11 @@
       </c>
     </row>
     <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B107" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1887,7 +2292,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Nanacamilpa de Mariano Arista</t>
+          <t>Nanacamilpa De Mariano Arista</t>
         </is>
       </c>
       <c r="C108">
@@ -1898,6 +2303,11 @@
       </c>
     </row>
     <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B109" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1929,6 +2339,11 @@
       </c>
     </row>
     <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B111" t="inlineStr">
         <is>
           <t>Veracruz</t>
@@ -1942,6 +2357,11 @@
       </c>
     </row>
     <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B112" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1973,6 +2393,11 @@
       </c>
     </row>
     <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Yucatán</t>
+        </is>
+      </c>
       <c r="B114" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2004,6 +2429,11 @@
       </c>
     </row>
     <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B116" t="inlineStr">
         <is>
           <t>Ojocaliente</t>
@@ -2017,6 +2447,11 @@
       </c>
     </row>
     <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B117" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2040,41 +2475,6 @@
       </c>
       <c r="D118">
         <v>1</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 1,114,005</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Junio de 2016</t>
-        </is>
       </c>
     </row>
   </sheetData>
